--- a/新品复盘/新品周报数据表_5.21-5.27.xlsx
+++ b/新品复盘/新品周报数据表_5.21-5.27.xlsx
@@ -551,11 +551,11 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>环比24.9%</t>
+          <t>上周185 | 环比24.9%</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>$17,618.93</t>
+          <t>$24,943.46</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>环比41.6%</t>
+          <t>上周$17,618.93 | 环比41.6%</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Y:48 N:26 未:11</t>
+          <t>Y:30 N:18 未:5</t>
         </is>
       </c>
     </row>
@@ -634,11 +634,11 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>无对手55</t>
+          <t>无对手87</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
     </row>
@@ -688,11 +688,11 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>占有对手SKU的87.1%</t>
+          <t>占有对手SKU的90.6%</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>有对手85+无对手55</t>
+          <t>有对手53+无对手87</t>
         </is>
       </c>
     </row>
@@ -982,10 +982,10 @@
         <v>11</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -998,13 +998,13 @@
         <v>24</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -1017,13 +1017,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1036,10 +1036,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>6</v>
@@ -1055,13 +1055,13 @@
         <v>32</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1074,13 +1074,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1093,13 +1093,13 @@
         <v>2</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>33.2%</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -2295,11 +2295,11 @@
         <v>103</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2347,11 +2347,11 @@
         <v>31</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>134</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2821,7 +2821,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1658</t>
+          <t>LYAP-X1800-1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>朱培源</t>
+          <t>胡煜星</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>$420.00</t>
+          <t>$40.00</t>
         </is>
       </c>
       <c r="H2" s="3" t="n">
@@ -2877,51 +2877,51 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>单链接PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2527</t>
+          <t>LYAP-X2190-L</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>饰条</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>$627.10</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -2957,39 +2957,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1800S-1L</t>
+          <t>LYAP-X2148-1R</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>饰条</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>$42.68</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -3025,17 +3025,17 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1800S-1R</t>
+          <t>MD-002-FR</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -3044,20 +3044,20 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>$88.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -3071,44 +3071,44 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
+          <t>无市场</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>竞争无优势</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>单链接PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2190-L</t>
+          <t>MD-001-FL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>饰条</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>本期不分析</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -3144,52 +3144,52 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>竞争无优势</t>
+          <t>本期不分析</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>单链接PLP+PLG同开</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2148-1L</t>
+          <t>LYAP-X2144-1L</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>王偲涵</t>
+          <t>朱培源</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>饰条</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>$68.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -3217,29 +3217,29 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1651-1L</t>
+          <t>LYAP-X2144-1R</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>俞东旭</t>
+          <t>朱培源</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -3248,16 +3248,16 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>$300.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -3297,39 +3297,39 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2429</t>
+          <t>LYAP-X2077</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>朱培源</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>$72.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -3343,34 +3343,34 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>链接优化</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1665-2R</t>
+          <t>LYAP-X2085</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -3406,22 +3406,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>未出单</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>广告-PLP</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -3433,26 +3433,26 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1788-BN</t>
+          <t>LYAM-X2804</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>俞东旭</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>牌照板支架</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>$29.99</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>广告-PLG</t>
+          <t>链接优化</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
@@ -3494,19 +3494,19 @@
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1929</t>
+          <t>LYAP-X2316</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3516,24 +3516,24 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>机盖及附件</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>$350.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>未出单</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>链接优化</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -3569,17 +3569,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>LYAM-X2428-BK</t>
+          <t>LYAM-X2452-SL</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>俞东旭</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -3588,21 +3588,21 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-100.0%</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-66.7%</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>$119.00</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>0%</t>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -3630,29 +3630,29 @@
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2320</t>
+          <t>LYAM-X3058</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>朱培源</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>挡泥板</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>未出单</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -3693,38 +3693,38 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2324</t>
+          <t>LYAM-X2414-SL</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -3733,11 +3733,11 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>$300.00</t>
+          <t>$105.00</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -3746,49 +3746,49 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>广告-PLP</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单链接PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2317-R</t>
+          <t>LYAM-X2452-BK</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -3796,16 +3796,16 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>$60.00</t>
+          <t>$100.00</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -3819,57 +3819,57 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>无调整</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>单链接PLP+PLG同开</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2318</t>
+          <t>LYAP-385</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>章鹏</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>挡泥板</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$71.00</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -3882,53 +3882,53 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>无市场</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>广告-PLP</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2385</t>
+          <t>LYAM-X2438-BK</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>朱培源</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>$240.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
@@ -3950,49 +3950,49 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>未出单</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>站外出单</t>
+          <t>未上架</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>未出单</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2428-3</t>
+          <t>LYAM-X2444</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>俞东旭</t>
+          <t>章鹏</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -4023,70 +4023,70 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>未上架</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>无调整</t>
+          <t>未出单</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>无广告</t>
+          <t>单PLP</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2412</t>
+          <t>LYAP-X1934</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>王偲涵</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>挡泥板</t>
+          <t>饰条</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$101.13</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>降价测试-市场有低价对手出单</t>
+          <t>无异常</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -4113,7 +4113,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1966</t>
+          <t>LYAP-X2412</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>朱培源</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -4132,66 +4132,66 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>-60.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>$258.00</t>
+          <t>$0.00</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>降价测试-市场有低价对手出单</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1957</t>
+          <t>LYAP-X1911-C</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>朱培源</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4204,20 +4204,20 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>$139.00</t>
+          <t>$73.99</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -4232,80 +4232,80 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>无调整</t>
+          <t>无异常</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单链接PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2025</t>
+          <t>MD-001-RL</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>章鹏</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$580.00</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -4317,22 +4317,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LYAM-X2433-SL</t>
+          <t>LYAP-X2210-C</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>俞东旭</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>车身外扩件</t>
+          <t>机盖及附件</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -4345,20 +4345,20 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>$250.00</t>
+          <t>$178.00</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -4368,60 +4368,60 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>广告-PLP</t>
+          <t>无异常</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1916-L</t>
+          <t>LYAP-X1800S-1L</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>章鹏</t>
+          <t>胡煜星</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>饰条</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>$380.00</t>
+          <t>$42.68</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4441,29 +4441,29 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>单链接PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1660-2R</t>
+          <t>LYAM-X2254-L</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>王偲涵</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -4472,34 +4472,34 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$83.53</t>
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>未出单</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4509,38 +4509,38 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>无广告</t>
+          <t>单PLP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>LYAM-X2445</t>
+          <t>MD-002-FL</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>车身外扩件</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -4549,88 +4549,88 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$957.00</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>未出单</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2210-BK</t>
+          <t>LYAP-X1788-BN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>机盖及附件</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>$214.00</t>
+          <t>$29.99</t>
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -4650,50 +4650,50 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1676</t>
+          <t>LYAM-X2428-BK</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$119.00</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -4713,38 +4713,38 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MD-001-FR</t>
+          <t>LYAM-X2862</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>俞东旭</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>机盖及附件</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -4753,15 +4753,15 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>$1,789.00</t>
+          <t>$135.00</t>
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4793,22 +4793,22 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2309</t>
+          <t>LYAP-X1651-1L</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -4816,20 +4816,20 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>$99.00</t>
+          <t>$300.00</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>站外出单</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -4861,12 +4861,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2319</t>
+          <t>LYAP-X2470</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -4889,20 +4889,20 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$96.00</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>未出单</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4912,29 +4912,29 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>无调整</t>
+          <t>广告-PLG</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>站外出单</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2317-L</t>
+          <t>LYAP-X1800S-1R</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4944,28 +4944,28 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>$120.00</t>
+          <t>$88.00</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -4975,34 +4975,34 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>无调整</t>
+          <t>无异常</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>单链接PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LYAM-X2896</t>
+          <t>LYAP-X2210-BK</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5012,38 +5012,38 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>饰条</t>
+          <t>机盖及附件</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>$139.00</t>
+          <t>$214.00</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5053,24 +5053,24 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1878</t>
+          <t>LYAP-X1927</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -5080,33 +5080,33 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>挡泥板</t>
+          <t>机盖及附件</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>$118.00</t>
+          <t>$336.00</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -5126,55 +5126,55 @@
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>单PLG</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LYAM-X2452-SL</t>
+          <t>LYAP-X2504</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>王偲涵</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>车身外扩件</t>
+          <t>挡泥板</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$315.00</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>广告-PLG</t>
+          <t>无异常</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -5194,50 +5194,50 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2470</t>
+          <t>LYAP-X1788-GR</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>$96.00</t>
+          <t>$287.20</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>广告-PLG</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
@@ -5262,14 +5262,14 @@
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1658L</t>
+          <t>LYAP-X1877</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -5284,28 +5284,28 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>挡泥板</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$172.00</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5315,34 +5315,34 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>无广告</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X1911-C</t>
+          <t>LYAP-X2170</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -5365,15 +5365,15 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>$73.99</t>
+          <t>$142.00</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
@@ -5383,29 +5383,29 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
           <t>竞争无优势</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>单链接PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1934</t>
+          <t>LYAP-X1911-BK</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -5420,75 +5420,75 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>饰条</t>
+          <t>机盖及附件</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>$101.13</t>
+          <t>$85.00</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
           <t>竞争无优势</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>LYAM-X2862</t>
+          <t>MD-002-RL</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>机盖及附件</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>$135.00</t>
+          <t>$480.00</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
@@ -5534,50 +5534,50 @@
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2317</t>
+          <t>MD-001-FR</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>$582.20</t>
+          <t>$1,789.00</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5587,48 +5587,48 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
+          <t>无市场</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
           <t>竞争无优势</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2314</t>
+          <t>LYAP-X1878</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>挡泥板</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -5637,52 +5637,52 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>$300.00</t>
+          <t>$118.00</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>站外出单</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>广告-PLP</t>
+          <t>无异常</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单PLG</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2428-1</t>
+          <t>LYAM-X2428-C</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
@@ -5705,15 +5705,15 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>$490.00</t>
+          <t>$250.00</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -5733,19 +5733,19 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>无广告</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2310-L</t>
+          <t>LYAP-X1360-1L</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -5755,116 +5755,116 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>章鹏</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>饰条</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$142.98</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>无异常</t>
+          <t>链接优化</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>单PLP</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LYAM-X3058</t>
+          <t>LYAM-X2414-BK</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>朱培源</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>挡泥板</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$190.00</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>未出单</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>无市场</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>广告-PLG</t>
+          <t>广告-PLP</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5881,22 +5881,22 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2310</t>
+          <t>LYAM-X2430-BK</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>胡煜星</t>
+          <t>王偲涵</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车身外扩件</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -5904,20 +5904,20 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>$117.00</t>
+          <t>$120.00</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>无市场</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -5949,53 +5949,53 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X1872</t>
+          <t>LYAP-X2308</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>张潇</t>
+          <t>胡煜星</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>挡泥板</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>$129.00</t>
+          <t>$601.00</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -6005,38 +6005,38 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>PLP+PLG同开</t>
+          <t>单链接PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2042-FR</t>
+          <t>MD-001-RR</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>王偲涵</t>
+          <t>俞东旭</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>车门系统</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -6045,15 +6045,15 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$1,779.00</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
@@ -6068,29 +6068,29 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>广告-PLG</t>
+          <t>无调整</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>站外出单</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>无广告</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LYAP-X2289</t>
+          <t>LYAP-X2190-R</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -6104,34 +6104,34 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>$456.00</t>
+          <t>$74.86</t>
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -6153,43 +6153,43 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>LYAP-X2523</t>
+          <t>LYAP-X1929</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>朱培源</t>
+          <t>张潇</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>车门系统</t>
+          <t>机盖及附件</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>$266.00</t>
+          <t>$350.00</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -6209,1674 +6209,42 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>站外出单</t>
+          <t>竞争无优势</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>无广告</t>
+          <t>PLP+PLG同开</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>MD-001-RL</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>$580.00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>无调整</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="inlineStr">
-        <is>
-          <t>PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>LYAM-X2433-BK</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>车身外扩件</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>150.0%</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>$575.00</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>广告-PLP</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>单PLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>MD-001-FL</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>42.3%</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>本期不分析</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>本期不分析</t>
-        </is>
-      </c>
-      <c r="M54" s="3" t="inlineStr">
-        <is>
-          <t>本期不分析</t>
-        </is>
-      </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X1788-GR</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>$287.20</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>无调整</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>单PLG</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X1660-2L</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>王偲涵</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>未出单</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="N56" s="3" t="inlineStr">
-        <is>
-          <t>无广告</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X2428-2</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>-66.7%</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>$250.00</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>45.2%</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>无调整</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t>无广告</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>LYAM-X2430-BK</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>王偲涵</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>车身外扩件</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>$120.00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>单PLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X2148-1R</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>王偲涵</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>饰条</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>48.9%</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>单链接PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X1800-1</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>胡煜星</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>$40.00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N60" s="3" t="inlineStr">
-        <is>
-          <t>单链接PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X1651-1R</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>站外出单</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>站外出单</t>
-        </is>
-      </c>
-      <c r="N61" s="5" t="inlineStr">
-        <is>
-          <t>单PLG</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X1808</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>胡煜星</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>-85.7%</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>$145.00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N62" s="3" t="inlineStr">
-        <is>
-          <t>无广告</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X1879</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>朱培源</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>挡泥板</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>$89.00</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N63" s="5" t="inlineStr">
-        <is>
-          <t>单链接PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X2130-1</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>张潇</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>站外出单</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>站外出单</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="inlineStr">
-        <is>
-          <t>无广告</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-838</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>张潇</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>饰条</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>-75.0%</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>$85.50</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X2310-R</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>胡煜星</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>广告-PLG</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
-          <t>单PLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X2472</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>张潇</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr">
-        <is>
-          <t>单PLG</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X1960</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>朱培源</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>挡泥板</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>$450.00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>广告-PLP</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="inlineStr">
-        <is>
-          <t>单PLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>LYAM-X2980-GR</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>胡煜星</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>车身外扩件</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="N69" s="5" t="inlineStr">
-        <is>
-          <t>无广告</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X2170</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>张潇</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>机盖及附件</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>$142.00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N70" s="3" t="inlineStr">
-        <is>
-          <t>单PLG</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>MD-002-FL</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>$957.00</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L71" s="5" t="inlineStr">
-        <is>
-          <t>无调整</t>
-        </is>
-      </c>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N71" s="5" t="inlineStr">
-        <is>
-          <t>单PLG</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X1909</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>朱培源</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>机盖及附件</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>-87.5%</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>$70.00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>64.3%</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>降价测试-市场无对手</t>
-        </is>
-      </c>
-      <c r="M72" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N72" s="3" t="inlineStr">
-        <is>
-          <t>单PLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>LYAP-X2190-R</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>张潇</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>饰条</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>$74.86</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>竞争无优势</t>
-        </is>
-      </c>
-      <c r="N73" s="5" t="inlineStr">
-        <is>
-          <t>PLP+PLG同开</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>LYAP-X1665-2L</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>俞东旭</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>车门系统</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>$255.00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>无异常</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
-          <t>无广告</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>LYAM-X2460</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>王偲涵</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>车身外扩件</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>未出单</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>无市场</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>链接优化</t>
-        </is>
-      </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>站外出单</t>
-        </is>
-      </c>
-      <c r="N75" s="5" t="inlineStr">
-        <is>
-          <t>单PLP</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>合计(74条)</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr"/>
-      <c r="C76" s="7" t="inlineStr"/>
-      <c r="D76" s="7" t="inlineStr"/>
-      <c r="E76" s="7" t="n">
-        <v>116</v>
-      </c>
-      <c r="F76" s="7" t="inlineStr"/>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>$13,089.65</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="n">
-        <v>462</v>
-      </c>
-      <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="7" t="inlineStr"/>
-      <c r="K76" s="7" t="inlineStr"/>
-      <c r="L76" s="7" t="inlineStr"/>
-      <c r="M76" s="7" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>合计(50条)</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr"/>
+      <c r="C52" s="7" t="inlineStr"/>
+      <c r="D52" s="7" t="inlineStr"/>
+      <c r="E52" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>$10,546.36</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>204</v>
+      </c>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10200,11 +8568,11 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -10268,11 +8636,11 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -10340,7 +8708,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -10404,11 +8772,11 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -10472,11 +8840,11 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -10608,11 +8976,11 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -10676,11 +9044,11 @@
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -10744,11 +9112,11 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -10812,11 +9180,11 @@
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -10880,11 +9248,11 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -10948,11 +9316,11 @@
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -11016,11 +9384,11 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -11084,11 +9452,11 @@
         </is>
       </c>
       <c r="I15" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -11152,11 +9520,11 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -11220,7 +9588,7 @@
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -11288,7 +9656,7 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -11360,7 +9728,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -11424,11 +9792,11 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -11492,11 +9860,11 @@
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -11560,11 +9928,11 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -11628,11 +9996,11 @@
         </is>
       </c>
       <c r="I23" s="5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -11696,11 +10064,11 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -11764,11 +10132,11 @@
         </is>
       </c>
       <c r="I25" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -11832,11 +10200,11 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -11900,11 +10268,11 @@
         </is>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -11968,11 +10336,11 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -12036,11 +10404,11 @@
         </is>
       </c>
       <c r="I29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -12104,11 +10472,11 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -12176,7 +10544,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -12308,11 +10676,11 @@
         </is>
       </c>
       <c r="I33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -12376,11 +10744,11 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -12444,11 +10812,11 @@
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -12512,11 +10880,11 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -12580,11 +10948,11 @@
         </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -12648,11 +11016,11 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -12716,11 +11084,11 @@
         </is>
       </c>
       <c r="I39" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -12784,11 +11152,11 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -12852,11 +11220,11 @@
         </is>
       </c>
       <c r="I41" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -12920,11 +11288,11 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -13056,11 +11424,11 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -13124,11 +11492,11 @@
         </is>
       </c>
       <c r="I45" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -13192,11 +11560,11 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -13328,11 +11696,11 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -13396,11 +11764,11 @@
         </is>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -13468,7 +11836,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -13532,11 +11900,11 @@
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -13600,11 +11968,11 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -13668,11 +12036,11 @@
         </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -13804,11 +12172,11 @@
         </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -13876,7 +12244,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -13940,11 +12308,11 @@
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -14008,7 +12376,7 @@
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -14076,11 +12444,11 @@
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -14144,11 +12512,11 @@
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -14212,7 +12580,7 @@
         </is>
       </c>
       <c r="I61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
@@ -14280,11 +12648,11 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -14352,7 +12720,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -14416,11 +12784,11 @@
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -14484,11 +12852,11 @@
         </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -14556,7 +12924,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
@@ -14688,11 +13056,11 @@
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -14756,11 +13124,11 @@
         </is>
       </c>
       <c r="I69" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
@@ -14824,11 +13192,11 @@
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -14892,11 +13260,11 @@
         </is>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -15028,11 +13396,11 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
@@ -15096,11 +13464,11 @@
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
@@ -15168,7 +13536,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -15232,11 +13600,11 @@
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
@@ -15300,11 +13668,11 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -15368,7 +13736,7 @@
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -15436,11 +13804,11 @@
         </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
@@ -15572,11 +13940,11 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
@@ -15644,7 +14012,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -15844,11 +14212,11 @@
         </is>
       </c>
       <c r="I85" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
@@ -15916,7 +14284,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
@@ -15980,11 +14348,11 @@
         </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -16048,11 +14416,11 @@
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -16116,11 +14484,11 @@
         </is>
       </c>
       <c r="I89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
@@ -16184,7 +14552,7 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -16252,11 +14620,11 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
@@ -16320,7 +14688,7 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -16388,11 +14756,11 @@
         </is>
       </c>
       <c r="I93" s="5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
@@ -16456,11 +14824,11 @@
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -16524,11 +14892,11 @@
         </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
@@ -16592,11 +14960,11 @@
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
@@ -16660,11 +15028,11 @@
         </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
@@ -16728,11 +15096,11 @@
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
@@ -16796,11 +15164,11 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
@@ -16864,11 +15232,11 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
@@ -16932,11 +15300,11 @@
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
@@ -17000,11 +15368,11 @@
         </is>
       </c>
       <c r="I102" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
@@ -17068,11 +15436,11 @@
         </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
@@ -17136,7 +15504,7 @@
         </is>
       </c>
       <c r="I104" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -17204,7 +15572,7 @@
         </is>
       </c>
       <c r="I105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
@@ -17272,11 +15640,11 @@
         </is>
       </c>
       <c r="I106" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
@@ -17340,11 +15708,11 @@
         </is>
       </c>
       <c r="I107" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr">
@@ -17476,11 +15844,11 @@
         </is>
       </c>
       <c r="I109" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
@@ -17548,7 +15916,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
@@ -17612,11 +15980,11 @@
         </is>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
@@ -17680,11 +16048,11 @@
         </is>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -17748,11 +16116,11 @@
         </is>
       </c>
       <c r="I113" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
@@ -17816,11 +16184,11 @@
         </is>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
@@ -17952,7 +16320,7 @@
         </is>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -18024,7 +16392,7 @@
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
@@ -18360,11 +16728,11 @@
         </is>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
@@ -18432,7 +16800,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
@@ -18496,11 +16864,11 @@
         </is>
       </c>
       <c r="I124" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr">
@@ -18564,11 +16932,11 @@
         </is>
       </c>
       <c r="I125" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
@@ -18632,11 +17000,11 @@
         </is>
       </c>
       <c r="I126" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr">
@@ -18700,11 +17068,11 @@
         </is>
       </c>
       <c r="I127" s="5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
@@ -18768,11 +17136,11 @@
         </is>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
@@ -18836,11 +17204,11 @@
         </is>
       </c>
       <c r="I129" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
@@ -18904,7 +17272,7 @@
         </is>
       </c>
       <c r="I130" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -19040,11 +17408,11 @@
         </is>
       </c>
       <c r="I132" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -19112,7 +17480,7 @@
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
@@ -19176,11 +17544,11 @@
         </is>
       </c>
       <c r="I134" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
@@ -19248,7 +17616,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
@@ -19316,7 +17684,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
@@ -19384,7 +17752,7 @@
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
@@ -19448,7 +17816,7 @@
         </is>
       </c>
       <c r="I138" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -19700,7 +18068,7 @@
         </is>
       </c>
       <c r="I142" s="7" t="n">
-        <v>475</v>
+        <v>208</v>
       </c>
       <c r="J142" s="7" t="inlineStr"/>
       <c r="K142" s="7" t="inlineStr"/>
